--- a/data/trans_orig/P6905-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P6905-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7284</t>
+          <t>7627</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20143</t>
+          <t>20267</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6719</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15215</t>
+          <t>15378</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16983</t>
+          <t>17168</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32851</t>
+          <t>32766</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>49,62%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26029</t>
+          <t>25905</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38888</t>
+          <t>38545</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4644</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13140</t>
+          <t>13089</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33180</t>
+          <t>33265</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49048</t>
+          <t>48863</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>74,0%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38325</t>
+          <t>37386</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61990</t>
+          <t>61420</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26777</t>
+          <t>27534</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44760</t>
+          <t>44247</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>70413</t>
+          <t>70285</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>99984</t>
+          <t>99957</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,11%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>80301</t>
+          <t>80871</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>103966</t>
+          <t>104905</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>34515</t>
+          <t>35028</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>52498</t>
+          <t>51741</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>121582</t>
+          <t>121609</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>151153</t>
+          <t>151281</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,28%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24392</t>
+          <t>24470</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46324</t>
+          <t>44309</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17985</t>
+          <t>18082</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33560</t>
+          <t>34050</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46110</t>
+          <t>46690</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72847</t>
+          <t>71363</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,4%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79704</t>
+          <t>81719</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>101636</t>
+          <t>101558</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36482</t>
+          <t>35992</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52057</t>
+          <t>51960</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>123223</t>
+          <t>124707</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>149960</t>
+          <t>149380</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,19%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22451</t>
+          <t>23132</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42909</t>
+          <t>44014</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,82 +1777,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>39,61%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>12467</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>7119</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>18603</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>33,66%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>19,22%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>50,23%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>44828</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>32890</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>57207</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>30,26%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>38,62%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>12467</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>7271</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>18627</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>33,66%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>19,63%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>50,29%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>44828</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>34003</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>56935</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>30,26%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>22,95%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>38,43%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>68201</t>
+          <t>67096</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>88659</t>
+          <t>87978</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,82 +1890,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>60,39%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>79,18%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>24570</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>18434</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>29918</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>66,34%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>49,77%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>80,78%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>103319</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>90940</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>115257</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>69,74%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>61,38%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>79,79%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>24570</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>18410</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>29766</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>66,34%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>49,71%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>80,37%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>103319</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>91212</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>114144</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>69,74%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>61,57%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,8%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7098</t>
+          <t>7387</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19423</t>
+          <t>19296</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8918</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11423</t>
+          <t>11641</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25271</t>
+          <t>26367</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>44,1%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26459</t>
+          <t>26586</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38784</t>
+          <t>38495</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>4909</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11938</t>
+          <t>11935</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34520</t>
+          <t>33424</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48368</t>
+          <t>48150</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,53%</t>
         </is>
       </c>
     </row>
@@ -2791,97 +2791,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
           <t>821</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>821</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>821</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2904,97 +2904,97 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>120280</t>
+          <t>123771</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>163652</t>
+          <t>166150</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>77154</t>
+          <t>76002</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>104241</t>
+          <t>104901</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>209046</t>
+          <t>204964</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>259159</t>
+          <t>256786</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,08%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>308653</t>
+          <t>306155</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>352025</t>
+          <t>348534</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>115880</t>
+          <t>115220</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>142967</t>
+          <t>144119</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>433268</t>
+          <t>435641</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>483381</t>
+          <t>487463</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>70,4%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2012 (tasa de respuesta: 98,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1764</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>976</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6216</t>
+          <t>6982</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>959</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7466</t>
+          <t>7944</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>38,98%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8563</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10327</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9083</t>
+          <t>9080</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12917</t>
+          <t>12439</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19406</t>
+          <t>19424</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18610</t>
+          <t>19021</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36778</t>
+          <t>37565</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17160</t>
+          <t>16994</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33617</t>
+          <t>34296</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41139</t>
+          <t>40454</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65334</t>
+          <t>64729</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,2%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>49510</t>
+          <t>48723</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67678</t>
+          <t>67267</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33495</t>
+          <t>32816</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>49952</t>
+          <t>50118</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>88066</t>
+          <t>88671</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>112261</t>
+          <t>112946</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,63%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18604</t>
+          <t>18157</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35686</t>
+          <t>35490</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27044</t>
+          <t>26612</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45029</t>
+          <t>44520</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49802</t>
+          <t>50553</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74382</t>
+          <t>75928</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>44,53%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62190</t>
+          <t>62386</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>79272</t>
+          <t>79719</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27602</t>
+          <t>28111</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45587</t>
+          <t>46019</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>96125</t>
+          <t>94579</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>120705</t>
+          <t>119954</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>70,35%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14705</t>
+          <t>14504</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32973</t>
+          <t>31747</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8336</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22092</t>
+          <t>21523</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26880</t>
+          <t>26252</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48270</t>
+          <t>48429</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,83%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57078</t>
+          <t>58304</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>75346</t>
+          <t>75547</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19354</t>
+          <t>19923</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33110</t>
+          <t>33086</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>83227</t>
+          <t>83068</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>104617</t>
+          <t>105245</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>80,04%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4792</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14824</t>
+          <t>15625</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>4433</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14727</t>
+          <t>14319</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11565</t>
+          <t>11526</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25883</t>
+          <t>26696</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>41,46%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25981</t>
+          <t>25180</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36013</t>
+          <t>36717</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8862</t>
+          <t>9270</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18671</t>
+          <t>19156</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38512</t>
+          <t>37699</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52830</t>
+          <t>52869</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,1%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>69651</t>
+          <t>69688</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>102071</t>
+          <t>100601</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>74043</t>
+          <t>72440</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>103828</t>
+          <t>103677</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>150211</t>
+          <t>152744</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>195919</t>
+          <t>193169</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>35,76%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>223276</t>
+          <t>224746</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>255696</t>
+          <t>255659</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>111007</t>
+          <t>111158</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>140792</t>
+          <t>142395</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>344263</t>
+          <t>347013</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>389971</t>
+          <t>387438</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>71,72%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>971</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7763</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1778</t>
+          <t>1728</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7787</t>
+          <t>8559</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3897</t>
+          <t>3955</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13225</t>
+          <t>13659</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>47,44%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>9048</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16153</t>
+          <t>16180</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9865</t>
+          <t>9915</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15569</t>
+          <t>15135</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24897</t>
+          <t>24839</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,27%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13872</t>
+          <t>13312</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29357</t>
+          <t>30010</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14871</t>
+          <t>14957</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28040</t>
+          <t>27729</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31703</t>
+          <t>32264</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52622</t>
+          <t>53650</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,96%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>52215</t>
+          <t>51562</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67700</t>
+          <t>68260</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18251</t>
+          <t>18562</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31420</t>
+          <t>31334</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>75241</t>
+          <t>74213</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>96160</t>
+          <t>95599</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>74,77%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23056</t>
+          <t>22657</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43392</t>
+          <t>42815</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18610</t>
+          <t>18081</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34623</t>
+          <t>34187</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46854</t>
+          <t>46520</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73435</t>
+          <t>71878</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>38,94%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69731</t>
+          <t>70308</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>90067</t>
+          <t>90466</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36835</t>
+          <t>37271</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52848</t>
+          <t>53377</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111146</t>
+          <t>112703</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>137727</t>
+          <t>138061</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,8%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18834</t>
+          <t>19358</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36195</t>
+          <t>37450</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14323</t>
+          <t>15375</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30311</t>
+          <t>29682</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37339</t>
+          <t>37326</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61394</t>
+          <t>62200</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>42,16%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>55233</t>
+          <t>53978</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>72594</t>
+          <t>72070</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25796</t>
+          <t>26425</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>41784</t>
+          <t>40732</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>86141</t>
+          <t>85335</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>110196</t>
+          <t>110209</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,7%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>6549</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18966</t>
+          <t>18479</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9859</t>
+          <t>10386</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22540</t>
+          <t>21812</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19754</t>
+          <t>19554</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37881</t>
+          <t>38852</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>51,36%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25882</t>
+          <t>26369</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38552</t>
+          <t>38299</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8259</t>
+          <t>8987</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>20413</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37765</t>
+          <t>36794</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55892</t>
+          <t>56092</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>74,15%</t>
         </is>
       </c>
     </row>
@@ -8406,97 +8406,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1070</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1070</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8519,97 +8519,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
           <t>1880</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1880</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>810</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>1880</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>80193</t>
+          <t>78681</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>114490</t>
+          <t>112585</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>75682</t>
+          <t>74529</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>104613</t>
+          <t>104549</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>160012</t>
+          <t>162076</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>206249</t>
+          <t>208156</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,76%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>235511</t>
+          <t>237416</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>269808</t>
+          <t>271320</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>111685</t>
+          <t>111749</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>140616</t>
+          <t>141769</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>360050</t>
+          <t>358143</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>406287</t>
+          <t>404223</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,38%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2171</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1601</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11419</t>
+          <t>11477</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13025</t>
+          <t>12648</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>59,29%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13743</t>
+          <t>13722</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8308</t>
+          <t>8685</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19436</t>
+          <t>19691</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>92,31%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14879</t>
+          <t>14898</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36201</t>
+          <t>35403</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16150</t>
+          <t>15345</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31232</t>
+          <t>29963</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34765</t>
+          <t>35603</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61216</t>
+          <t>61069</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>56,02%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22873</t>
+          <t>23671</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44195</t>
+          <t>44176</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18717</t>
+          <t>19986</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33799</t>
+          <t>34604</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>47806</t>
+          <t>47953</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>74257</t>
+          <t>73419</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>67,34%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11818</t>
+          <t>11643</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27832</t>
+          <t>27919</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16352</t>
+          <t>16456</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29685</t>
+          <t>30189</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32342</t>
+          <t>32040</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53093</t>
+          <t>54524</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,87%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67699</t>
+          <t>67612</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83713</t>
+          <t>83888</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45867</t>
+          <t>45363</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59200</t>
+          <t>59096</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>117991</t>
+          <t>116560</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>138742</t>
+          <t>139044</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,27%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12749</t>
+          <t>12785</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29577</t>
+          <t>30097</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22247</t>
+          <t>21801</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62937</t>
+          <t>62471</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43974</t>
+          <t>42135</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85956</t>
+          <t>82771</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>31,41%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>78976</t>
+          <t>78456</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>95804</t>
+          <t>95768</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>92012</t>
+          <t>92478</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>132702</t>
+          <t>133148</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>177546</t>
+          <t>180731</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>219528</t>
+          <t>221367</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>84,01%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7993</t>
+          <t>8588</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21433</t>
+          <t>20724</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11110</t>
+          <t>11305</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20763</t>
+          <t>21355</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21610</t>
+          <t>21632</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37417</t>
+          <t>37386</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,41%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46003</t>
+          <t>46712</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>59443</t>
+          <t>58848</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34744</t>
+          <t>34152</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>44397</t>
+          <t>44202</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>85526</t>
+          <t>85557</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>101333</t>
+          <t>101311</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,4%</t>
         </is>
       </c>
     </row>
@@ -11385,97 +11385,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1016</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>894</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2370</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>34,87%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>81,35%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2365</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>34,87%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3097</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>17,41%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>81,16%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1016</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>3259</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>17,41%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>53,06%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>559</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -11568,7 +11568,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2577</t>
+          <t>2739</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -11583,7 +11583,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>60738</t>
+          <t>62196</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>99292</t>
+          <t>97889</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>83849</t>
+          <t>82978</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>135810</t>
+          <t>136476</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>160456</t>
+          <t>160841</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>218460</t>
+          <t>220170</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,74%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>240213</t>
+          <t>241616</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>278767</t>
+          <t>277309</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>218405</t>
+          <t>217739</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>270366</t>
+          <t>271237</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>475260</t>
+          <t>473550</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>533264</t>
+          <t>532879</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,81%</t>
         </is>
       </c>
     </row>
